--- a/03_Prompting/outputs/GPT/RESULT_f-droid_gpt-4o_fewshot.xlsx
+++ b/03_Prompting/outputs/GPT/RESULT_f-droid_gpt-4o_fewshot.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -9148,7 +9148,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -9913,7 +9913,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10219,7 +10219,7 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -11817,7 +11817,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12531,7 +12531,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12735,7 +12735,7 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12837,7 +12837,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12922,7 +12922,7 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -13347,7 +13347,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15404,7 +15404,7 @@
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -15472,7 +15472,7 @@
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15880,7 +15880,7 @@
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16951,7 +16951,7 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17767,7 +17767,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18192,7 +18192,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18328,7 +18328,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18651,7 +18651,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18872,7 +18872,7 @@
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -19161,7 +19161,7 @@
       </c>
       <c r="C1102" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -19756,7 +19756,7 @@
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -19858,7 +19858,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20045,7 +20045,7 @@
       </c>
       <c r="C1154" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="C1159" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20487,7 +20487,7 @@
       </c>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -25220,7 +25220,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -25884,7 +25884,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -29233,7 +29233,7 @@
       </c>
       <c r="C1694" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -29930,7 +29930,7 @@
       </c>
       <c r="C1735" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -29947,7 +29947,7 @@
       </c>
       <c r="C1736" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="C1791" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -33058,7 +33058,7 @@
       </c>
       <c r="C1919" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -34112,7 +34112,7 @@
       </c>
       <c r="C1981" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -34350,7 +34350,7 @@
       </c>
       <c r="C1995" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -35455,7 +35455,7 @@
       </c>
       <c r="C2060" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -36832,7 +36832,7 @@
       </c>
       <c r="C2141" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -36900,7 +36900,7 @@
       </c>
       <c r="C2145" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -37988,7 +37988,7 @@
       </c>
       <c r="C2209" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -38260,7 +38260,7 @@
       </c>
       <c r="C2225" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -38481,7 +38481,7 @@
       </c>
       <c r="C2238" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -39280,7 +39280,7 @@
       </c>
       <c r="C2285" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -40895,7 +40895,7 @@
       </c>
       <c r="C2380" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -41694,7 +41694,7 @@
       </c>
       <c r="C2427" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -43020,7 +43020,7 @@
       </c>
       <c r="C2505" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -43700,7 +43700,7 @@
       </c>
       <c r="C2545" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -46352,7 +46352,7 @@
       </c>
       <c r="C2701" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -48786,7 +48786,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6592749032030975</v>
+        <v>0.6420274551214361</v>
       </c>
     </row>
     <row r="3">
@@ -48796,7 +48796,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5600900906665303</v>
+        <v>0.5276516104541582</v>
       </c>
     </row>
     <row r="4">
@@ -48806,7 +48806,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5922203820516154</v>
+        <v>0.5634042886512974</v>
       </c>
     </row>
     <row r="5">
@@ -48816,7 +48816,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.767482663999243</v>
+        <v>0.7517164060006383</v>
       </c>
     </row>
     <row r="6">
@@ -48826,7 +48826,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6004432311817095</v>
+        <v>0.580060535674222</v>
       </c>
     </row>
     <row r="7">
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>870.8918605410001</v>
+        <v>1904.884817376995</v>
       </c>
     </row>
     <row r="8">
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3065441254984161</v>
+        <v>0.6704979997807091</v>
       </c>
     </row>
   </sheetData>
